--- a/src/lab05/data/people.xlsx
+++ b/src/lab05/data/people.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,6 +415,11 @@
   </sheetPr>
   <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
